--- a/compressed_data_classification/src/models/best_models_result/resultados_modelos_original_data.xlsx
+++ b/compressed_data_classification/src/models/best_models_result/resultados_modelos_original_data.xlsx
@@ -476,41 +476,41 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'mlp__activation': 'relu', 'mlp__alpha': 0.0001, 'mlp__early_stopping': True, 'mlp__hidden_layer_sizes': (20, 10), 'mlp__learning_rate': 'constant', 'mlp__learning_rate_init': 0.001, 'mlp__max_iter': 5000, 'mlp__solver': 'adam'}</t>
+          <t>{'mlp__activation': 'identity', 'mlp__alpha': 0.0001, 'mlp__early_stopping': True, 'mlp__hidden_layer_sizes': (15, 10), 'mlp__learning_rate': 'constant', 'mlp__learning_rate_init': 0.001, 'mlp__max_iter': 5000, 'mlp__solver': 'adam'}</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7035</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9724</v>
+        <v>0.9932</v>
       </c>
       <c r="E2" t="n">
-        <v>21.9188</v>
+        <v>8.812900000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.73      0.97      0.83        99
-           1       0.53      0.31      0.39       104
-           2       0.55      0.65      0.60       112
-           3       0.75      0.93      0.83        86
-           4       0.72      0.73      0.72        88
-           5       0.74      0.60      0.66        98
-           6       0.84      0.91      0.88       101
-           7       0.73      0.59      0.65        94
-           8       0.73      0.68      0.70        99
-           9       0.95      1.00      0.98       105
-          10       0.60      0.76      0.67       121
-          11       0.51      0.39      0.45        99
-          12       0.85      0.73      0.79        94
-          13       0.84      0.97      0.90        97
-          14       0.39      0.22      0.28       102
-          15       0.78      0.74      0.76        91
-          16       0.60      0.82      0.69       110
-    accuracy                           0.70      1700
-   macro avg       0.70      0.71      0.69      1700
-weighted avg       0.69      0.70      0.69      1700
+           0       0.99      0.99      0.99        99
+           1       0.60      0.82      0.69       104
+           2       0.96      0.97      0.97       112
+           3       0.95      1.00      0.97        86
+           4       0.90      0.95      0.93        88
+           5       0.92      0.95      0.93        98
+           6       0.82      0.86      0.84       101
+           7       0.96      0.70      0.81        94
+           8       0.84      0.85      0.84        99
+           9       0.99      1.00      1.00       105
+          10       0.93      0.79      0.85       121
+          11       0.84      0.73      0.78        99
+          12       0.84      0.78      0.81        94
+          13       0.97      0.95      0.96        97
+          14       0.97      0.85      0.91       102
+          15       0.96      0.81      0.88        91
+          16       0.69      0.91      0.79       110
+    accuracy                           0.88      1700
+   macro avg       0.89      0.88      0.88      1700
+weighted avg       0.89      0.88      0.88      1700
 </t>
         </is>
       </c>
@@ -518,10 +518,10 @@
         <v>144</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9673</v>
+        <v>0.9911</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="3">
@@ -530,41 +530,41 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'svc_rbf__C': 10, 'svc_rbf__gamma': 0.001, 'svc_rbf__kernel': 'rbf', 'svc_rbf__probability': True, 'svc_rbf__random_state': 42}</t>
+          <t>{'svc_rbf__C': 1, 'svc_rbf__gamma': 0.001, 'svc_rbf__kernel': 'rbf', 'svc_rbf__probability': True, 'svc_rbf__random_state': 42}</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7747000000000001</v>
+        <v>0.9335</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9816</v>
+        <v>0.9972</v>
       </c>
       <c r="E3" t="n">
-        <v>16.5541</v>
+        <v>3.2682</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.85      0.99      0.92        99
-           1       0.63      0.66      0.65       104
-           2       0.69      0.73      0.71       112
-           3       0.84      0.93      0.88        86
-           4       0.75      0.69      0.72        88
-           5       0.79      0.77      0.78        98
-           6       0.92      0.94      0.93       101
-           7       0.77      0.67      0.72        94
-           8       0.68      0.64      0.66        99
-           9       0.99      1.00      1.00       105
-          10       0.90      0.86      0.88       121
-          11       0.63      0.58      0.60        99
-          12       0.68      0.67      0.68        94
+           0       0.99      1.00      0.99        99
+           1       0.93      0.97      0.95       104
+           2       0.98      0.99      0.99       112
+           3       1.00      0.97      0.98        86
+           4       0.93      0.93      0.93        88
+           5       0.95      0.93      0.94        98
+           6       0.98      0.91      0.94       101
+           7       0.99      0.86      0.92        94
+           8       0.82      0.91      0.86        99
+           9       1.00      1.00      1.00       105
+          10       0.97      0.98      0.98       121
+          11       0.97      0.85      0.90        99
+          12       0.69      0.87      0.77        94
           13       0.99      1.00      0.99        97
-          14       0.54      0.42      0.47       102
-          15       0.79      0.63      0.70        91
-          16       0.68      0.95      0.79       110
-    accuracy                           0.77      1700
-   macro avg       0.77      0.77      0.77      1700
-weighted avg       0.77      0.77      0.77      1700
+          14       1.00      0.93      0.96       102
+          15       0.92      0.77      0.84        91
+          16       0.86      0.95      0.91       110
+    accuracy                           0.93      1700
+   macro avg       0.94      0.93      0.93      1700
+weighted avg       0.94      0.93      0.93      1700
 </t>
         </is>
       </c>
@@ -572,10 +572,10 @@
         <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9792</v>
+        <v>0.9963</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0016</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="4">
@@ -588,37 +588,37 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.7694</v>
+        <v>0.9341</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9823</v>
+        <v>0.9974</v>
       </c>
       <c r="E4" t="n">
-        <v>17.8553</v>
+        <v>4.7324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.80      0.99      0.89        99
-           1       0.57      0.58      0.57       104
-           2       0.63      0.60      0.61       112
-           3       0.79      0.94      0.86        86
-           4       0.74      0.78      0.76        88
-           5       0.80      0.78      0.79        98
-           6       0.89      0.92      0.91       101
-           7       0.80      0.70      0.75        94
-           8       0.77      0.76      0.76        99
+           0       0.97      1.00      0.99        99
+           1       0.96      0.85      0.90       104
+           2       0.97      0.99      0.98       112
+           3       0.99      1.00      0.99        86
+           4       0.95      0.99      0.97        88
+           5       0.98      0.96      0.97        98
+           6       0.91      0.94      0.93       101
+           7       0.99      0.76      0.86        94
+           8       0.80      0.91      0.85        99
            9       0.99      1.00      1.00       105
-          10       0.80      0.79      0.79       121
-          11       0.68      0.51      0.58        99
-          12       0.93      0.73      0.82        94
-          13       0.98      1.00      0.99        97
-          14       0.46      0.40      0.43       102
-          15       0.86      0.73      0.79        91
-          16       0.65      0.91      0.75       110
-    accuracy                           0.77      1700
-   macro avg       0.77      0.77      0.77      1700
-weighted avg       0.77      0.77      0.77      1700
+          10       0.95      0.93      0.94       121
+          11       0.93      0.94      0.93        99
+          12       0.96      0.85      0.90        94
+          13       0.99      1.00      0.99        97
+          14       1.00      0.95      0.97       102
+          15       0.95      0.88      0.91        91
+          16       0.72      0.94      0.81       110
+    accuracy                           0.93      1700
+   macro avg       0.94      0.93      0.94      1700
+weighted avg       0.94      0.93      0.93      1700
 </t>
         </is>
       </c>
@@ -626,10 +626,10 @@
         <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9822</v>
+        <v>0.9971</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001</v>
+        <v>0.0005999999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/compressed_data_classification/src/models/best_models_result/resultados_modelos_original_data.xlsx
+++ b/compressed_data_classification/src/models/best_models_result/resultados_modelos_original_data.xlsx
@@ -629,7 +629,7 @@
         <v>0.9971</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0005</v>
       </c>
     </row>
   </sheetData>

--- a/compressed_data_classification/src/models/best_models_result/resultados_modelos_original_data.xlsx
+++ b/compressed_data_classification/src/models/best_models_result/resultados_modelos_original_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,121 +471,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'mlp__activation': 'relu', 'mlp__alpha': 0.01, 'mlp__early_stopping': True, 'mlp__hidden_layer_sizes': (20, 10), 'mlp__learning_rate': 'constant', 'mlp__learning_rate_init': 0.001, 'mlp__max_iter': 5000, 'mlp__solver': 'sgd'}</t>
+          <t>{'qsvc__decision_function_shape': 'ovr', 'qsvc__probability': True}</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.0576</v>
+        <v>0.7252999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5</v>
+        <v>0.9832</v>
       </c>
       <c r="E2" t="n">
-        <v>33.3541</v>
+        <v>19.8941</v>
       </c>
       <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.00      0.00      0.00        99
-           1       0.00      0.00      0.00       104
-           2       0.00      0.00      0.00       112
-           3       0.00      0.00      0.00        86
-           4       0.00      0.00      0.00        88
-           5       0.06      1.00      0.11        98
-           6       0.00      0.00      0.00       101
-           7       0.00      0.00      0.00        94
-           8       0.00      0.00      0.00        99
-           9       0.00      0.00      0.00       105
-          10       0.00      0.00      0.00       121
-          11       0.00      0.00      0.00        99
-          12       0.00      0.00      0.00        94
-          13       0.00      0.00      0.00        97
-          14       0.00      0.00      0.00       102
-          15       0.00      0.00      0.00        91
-          16       0.00      0.00      0.00       110
-    accuracy                           0.06      1700
-   macro avg       0.00      0.06      0.01      1700
-weighted avg       0.00      0.06      0.01      1700
-</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.0003</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>{'svc_rbf__C': 1, 'svc_rbf__gamma': 0.01, 'svc_rbf__kernel': 'rbf', 'svc_rbf__probability': True, 'svc_rbf__random_state': 42}</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.6624</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.988</v>
-      </c>
-      <c r="E3" t="n">
-        <v>21.62</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              precision    recall  f1-score   support
-           0       1.00      1.00      1.00        99
-           1       0.95      0.77      0.85       104
-           2       0.99      0.87      0.92       112
-           3       1.00      0.62      0.76        86
-           4       0.94      0.36      0.52        88
-           5       0.97      0.31      0.47        98
-           6       0.99      0.66      0.79       101
-           7       0.91      0.52      0.66        94
-           8       0.86      0.44      0.59        99
-           9       1.00      1.00      1.00       105
-          10       1.00      0.88      0.94       121
-          11       0.96      0.25      0.40        99
-          12       0.53      0.21      0.30        94
-          13       1.00      0.97      0.98        97
-          14       1.00      0.37      0.54       102
-          15       0.14      0.98      0.25        91
-          16       0.94      0.88      0.91       110
-    accuracy                           0.66      1700
-   macro avg       0.89      0.65      0.70      1700
-weighted avg       0.90      0.66      0.71      1700
-</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>0.6415</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.016</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>{'qsvc__probability': True}</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.7252999999999999</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.9832</v>
-      </c>
-      <c r="E4" t="n">
-        <v>19.8941</v>
-      </c>
-      <c r="F4" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
            0       0.88      1.00      0.93        99
@@ -611,10 +509,10 @@
 </t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="G2" t="n">
         <v>0.7139</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H2" t="n">
         <v>0.0125</v>
       </c>
     </row>

--- a/compressed_data_classification/src/models/best_models_result/resultados_modelos_original_data.xlsx
+++ b/compressed_data_classification/src/models/best_models_result/resultados_modelos_original_data.xlsx
@@ -471,49 +471,49 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'qsvc__decision_function_shape': 'ovr', 'qsvc__probability': True}</t>
+          <t>{'qsvc__C': 1, 'qsvc__coef0': 1, 'qsvc__decision_function_shape': 'ovo', 'qsvc__degree': 2, 'qsvc__gamma': 'scale', 'qsvc__kernel': 'poly', 'qsvc__probability': True}</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7252999999999999</v>
+        <v>0.7729</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9832</v>
+        <v>0.9879</v>
       </c>
       <c r="E2" t="n">
-        <v>19.8941</v>
+        <v>16.0312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.88      1.00      0.93        99
-           1       0.46      0.68      0.55       104
-           2       0.78      0.62      0.69       112
-           3       0.72      0.91      0.80        86
-           4       0.76      0.91      0.83        88
-           5       0.79      0.92      0.85        98
-           6       0.84      0.86      0.85       101
-           7       0.72      0.62      0.67        94
-           8       0.67      0.73      0.70        99
-           9       0.99      1.00      1.00       105
-          10       0.50      0.20      0.28       121
-          11       0.93      0.71      0.80        99
-          12       1.00      0.45      0.62        94
-          13       0.71      0.53      0.60        97
-          14       0.98      0.80      0.88       102
-          15       0.89      0.64      0.74        91
-          16       0.42      0.88      0.57       110
-    accuracy                           0.73      1700
-   macro avg       0.77      0.73      0.73      1700
-weighted avg       0.76      0.73      0.72      1700
+           0       0.89      1.00      0.94        99
+           1       0.52      0.73      0.61       104
+           2       0.86      0.81      0.83       112
+           3       0.78      0.97      0.86        86
+           4       0.79      0.93      0.85        88
+           5       0.87      0.94      0.90        98
+           6       0.84      0.87      0.85       101
+           7       0.78      0.66      0.71        94
+           8       0.67      0.81      0.73        99
+           9       0.97      1.00      0.99       105
+          10       0.66      0.31      0.42       121
+          11       0.94      0.76      0.84        99
+          12       1.00      0.60      0.75        94
+          13       0.85      0.64      0.73        97
+          14       1.00      0.78      0.88       102
+          15       1.00      0.53      0.69        91
+          16       0.46      0.88      0.60       110
+    accuracy                           0.77      1700
+   macro avg       0.81      0.78      0.78      1700
+weighted avg       0.81      0.77      0.77      1700
 </t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.7139</v>
+        <v>0.7607</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0125</v>
+        <v>0.0139</v>
       </c>
     </row>
   </sheetData>

--- a/compressed_data_classification/src/models/best_models_result/resultados_modelos_original_data.xlsx
+++ b/compressed_data_classification/src/models/best_models_result/resultados_modelos_original_data.xlsx
@@ -425,43 +425,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>melhores_parametros</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
           <t>acuracia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>roc_auc_score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>mse</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>relatorio_classificacao</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>best_mean_score</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>std_best_score_k_fold</t>
         </is>
       </c>
     </row>
@@ -469,51 +454,40 @@
       <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>{'qsvc__C': 1, 'qsvc__coef0': 1, 'qsvc__decision_function_shape': 'ovo', 'qsvc__degree': 2, 'qsvc__gamma': 'scale', 'qsvc__kernel': 'poly', 'qsvc__probability': True}</t>
-        </is>
+      <c r="B2" t="n">
+        <v>0.9418</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7729</v>
+        <v>0.9976</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9879</v>
-      </c>
-      <c r="E2" t="n">
-        <v>16.0312</v>
-      </c>
-      <c r="F2" t="inlineStr">
+        <v>4.4659</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.89      1.00      0.94        99
-           1       0.52      0.73      0.61       104
-           2       0.86      0.81      0.83       112
-           3       0.78      0.97      0.86        86
-           4       0.79      0.93      0.85        88
-           5       0.87      0.94      0.90        98
-           6       0.84      0.87      0.85       101
-           7       0.78      0.66      0.71        94
-           8       0.67      0.81      0.73        99
-           9       0.97      1.00      0.99       105
-          10       0.66      0.31      0.42       121
-          11       0.94      0.76      0.84        99
-          12       1.00      0.60      0.75        94
-          13       0.85      0.64      0.73        97
-          14       1.00      0.78      0.88       102
-          15       1.00      0.53      0.69        91
-          16       0.46      0.88      0.60       110
-    accuracy                           0.77      1700
-   macro avg       0.81      0.78      0.78      1700
-weighted avg       0.81      0.77      0.77      1700
+           0       0.99      1.00      0.99        99
+           1       0.95      0.84      0.89       104
+           2       0.98      0.99      0.99       112
+           3       1.00      1.00      1.00        86
+           4       0.97      0.99      0.98        88
+           5       0.99      0.99      0.99        98
+           6       0.92      0.94      0.93       101
+           7       0.97      0.79      0.87        94
+           8       0.83      0.92      0.88        99
+           9       0.99      1.00      1.00       105
+          10       0.95      0.93      0.94       121
+          11       0.94      0.93      0.93        99
+          12       0.97      0.88      0.92        94
+          13       0.99      1.00      0.99        97
+          14       1.00      0.96      0.98       102
+          15       0.95      0.92      0.94        91
+          16       0.73      0.93      0.82       110
+    accuracy                           0.94      1700
+   macro avg       0.95      0.94      0.94      1700
+weighted avg       0.95      0.94      0.94      1700
 </t>
         </is>
-      </c>
-      <c r="G2" t="n">
-        <v>0.7607</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.0139</v>
       </c>
     </row>
   </sheetData>

--- a/compressed_data_classification/src/models/best_models_result/resultados_modelos_original_data.xlsx
+++ b/compressed_data_classification/src/models/best_models_result/resultados_modelos_original_data.xlsx
@@ -455,33 +455,33 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9418</v>
+        <v>0.9412</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9976</v>
+        <v>0.9977</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4659</v>
+        <v>4.5541</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.99      1.00      0.99        99
-           1       0.95      0.84      0.89       104
-           2       0.98      0.99      0.99       112
+           0       0.98      1.00      0.99        99
+           1       0.96      0.84      0.89       104
+           2       0.97      0.99      0.98       112
            3       1.00      1.00      1.00        86
            4       0.97      0.99      0.98        88
            5       0.99      0.99      0.99        98
            6       0.92      0.94      0.93       101
-           7       0.97      0.79      0.87        94
+           7       0.97      0.78      0.86        94
            8       0.83      0.92      0.88        99
            9       0.99      1.00      1.00       105
           10       0.95      0.93      0.94       121
-          11       0.94      0.93      0.93        99
+          11       0.94      0.94      0.94        99
           12       0.97      0.88      0.92        94
           13       0.99      1.00      0.99        97
           14       1.00      0.96      0.98       102
-          15       0.95      0.92      0.94        91
+          15       0.95      0.91      0.93        91
           16       0.73      0.93      0.82       110
     accuracy                           0.94      1700
    macro avg       0.95      0.94      0.94      1700

--- a/compressed_data_classification/src/models/best_models_result/resultados_modelos_original_data.xlsx
+++ b/compressed_data_classification/src/models/best_models_result/resultados_modelos_original_data.xlsx
@@ -455,37 +455,37 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9412</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9977</v>
+        <v>0.9994</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5541</v>
+        <v>1.6135</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.98      1.00      0.99        99
-           1       0.96      0.84      0.89       104
-           2       0.97      0.99      0.98       112
+           0       1.00      1.00      1.00        99
+           1       0.91      0.97      0.94       104
+           2       0.98      0.99      0.99       112
            3       1.00      1.00      1.00        86
-           4       0.97      0.99      0.98        88
-           5       0.99      0.99      0.99        98
-           6       0.92      0.94      0.93       101
-           7       0.97      0.78      0.86        94
-           8       0.83      0.92      0.88        99
-           9       0.99      1.00      1.00       105
-          10       0.95      0.93      0.94       121
+           4       0.98      0.95      0.97        88
+           5       1.00      1.00      1.00        98
+           6       0.98      0.98      0.98       101
+           7       0.99      0.99      0.99        94
+           8       0.92      0.97      0.95        99
+           9       1.00      1.00      1.00       105
+          10       0.98      0.98      0.98       121
           11       0.94      0.94      0.94        99
-          12       0.97      0.88      0.92        94
+          12       1.00      0.89      0.94        94
           13       0.99      1.00      0.99        97
-          14       1.00      0.96      0.98       102
-          15       0.95      0.91      0.93        91
-          16       0.73      0.93      0.82       110
-    accuracy                           0.94      1700
-   macro avg       0.95      0.94      0.94      1700
-weighted avg       0.95      0.94      0.94      1700
+          14       0.98      0.96      0.97       102
+          15       0.99      0.93      0.96        91
+          16       0.96      1.00      0.98       110
+    accuracy                           0.98      1700
+   macro avg       0.98      0.97      0.98      1700
+weighted avg       0.98      0.98      0.98      1700
 </t>
         </is>
       </c>
